--- a/tasks/finalpool/terminal-sf-scholarly-excel-ppt-gcal/groundtruth_workspace/Sales_Strategy_Analysis.xlsx
+++ b/tasks/finalpool/terminal-sf-scholarly-excel-ppt-gcal/groundtruth_workspace/Sales_Strategy_Analysis.xlsx
@@ -20,13 +20,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,8 +52,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,32 +424,32 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>revenue</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>order_count</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>avg_order_value</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>yoy_change_pct</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>priority_tag</t>
         </is>
@@ -467,7 +471,7 @@
         <v>158.24</v>
       </c>
       <c r="E2" t="n">
-        <v>11.86</v>
+        <v>2.17</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -491,7 +495,7 @@
         <v>153.08</v>
       </c>
       <c r="E3" t="n">
-        <v>12.74</v>
+        <v>2.82</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -515,7 +519,7 @@
         <v>146.7</v>
       </c>
       <c r="E4" t="n">
-        <v>10.24</v>
+        <v>2.77</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -539,7 +543,7 @@
         <v>155.5</v>
       </c>
       <c r="E5" t="n">
-        <v>13.61</v>
+        <v>3.81</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -563,7 +567,7 @@
         <v>148.53</v>
       </c>
       <c r="E6" t="n">
-        <v>12.07</v>
+        <v>3.61</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -586,22 +590,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>segment</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>customer_count</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>total_spend</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>avg_ltv</t>
         </is>
@@ -620,7 +624,7 @@
         <v>839609.2</v>
       </c>
       <c r="D2" t="n">
-        <v>1670.15</v>
+        <v>1521.51</v>
       </c>
     </row>
     <row r="3">
@@ -636,7 +640,7 @@
         <v>793741.6899999999</v>
       </c>
       <c r="D3" t="n">
-        <v>1617.05</v>
+        <v>1465.45</v>
       </c>
     </row>
     <row r="4">
@@ -652,7 +656,7 @@
         <v>712686.66</v>
       </c>
       <c r="D4" t="n">
-        <v>1559.27</v>
+        <v>1430.82</v>
       </c>
     </row>
     <row r="5">
@@ -668,7 +672,7 @@
         <v>702960.78</v>
       </c>
       <c r="D5" t="n">
-        <v>1556.49</v>
+        <v>1396.28</v>
       </c>
     </row>
   </sheetData>
@@ -686,22 +690,22 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>paper_title</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>key_finding</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>applicable_region</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>expected_impact</t>
         </is>
@@ -810,27 +814,27 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>action</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>region</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>timeline</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>owner</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>research_basis</t>
         </is>
